--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604083</v>
       </c>
       <c r="B2" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604083</v>
       </c>
       <c r="B2" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604083</v>
       </c>
       <c r="B2" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604083</v>
       </c>
       <c r="B2" t="n">
-        <v>97525</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604083</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,3325 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129527700</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>569070</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6412584</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129527963</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>569023</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6412835</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129527842</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>569057</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6412642</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129527900</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>569029</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6412790</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129527787</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>569153</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6412439</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129527859</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>569043</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6412642</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129527942</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>569019</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6412827</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129528060</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>569004</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6412825</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129528042</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>568999</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6412827</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129527924</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>569016</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6412795</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129527714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>569077</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6412589</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129527906</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>569032</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6412788</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129527885</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>568987</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6412775</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129527808</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>569157</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6412484</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129528013</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92870</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>569019</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6412824</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129527636</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92203</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>569145</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6412521</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129528074</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>568997</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6412826</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129527910</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>569026</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6412804</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129527766</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>569036</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6412522</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129527872</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92203</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>569039</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6412677</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129528112</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58097</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>569104</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6412595</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129527753</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>569077</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6412532</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129527732</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>569083</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6412557</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129527675</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>569104</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6412595</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129528084</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>569002</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6412837</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129527981</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>569004</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6412822</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129527932</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92870</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>569016</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6412795</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129528002</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>569016</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6412840</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129528031</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>568997</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6412845</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129527952</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>569027</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6412813</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129527594</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>569183</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6412425</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Födosökt i stubbe</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -1645,7 +1645,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129528042</v>
+        <v>129527924</v>
       </c>
       <c r="B11" t="n">
         <v>98724</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568999</v>
+        <v>569016</v>
       </c>
       <c r="R11" t="n">
-        <v>6412827</v>
+        <v>6412795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129527924</v>
+        <v>129528042</v>
       </c>
       <c r="B12" t="n">
         <v>98724</v>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569016</v>
+        <v>568999</v>
       </c>
       <c r="R12" t="n">
-        <v>6412795</v>
+        <v>6412827</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2933,27 +2933,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129528112</v>
+        <v>129527732</v>
       </c>
       <c r="B23" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2964,7 +2964,11 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2972,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569104</v>
+        <v>569083</v>
       </c>
       <c r="R23" t="n">
-        <v>6412595</v>
+        <v>6412557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3008,6 +3012,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3034,42 +3043,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129527753</v>
+        <v>129528112</v>
       </c>
       <c r="B24" t="n">
-        <v>98724</v>
+        <v>58097</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3077,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569077</v>
+        <v>569104</v>
       </c>
       <c r="R24" t="n">
-        <v>6412532</v>
+        <v>6412595</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,7 +3126,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3140,42 +3144,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129527732</v>
+        <v>129527753</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>98724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3183,10 +3187,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569083</v>
+        <v>569077</v>
       </c>
       <c r="R25" t="n">
-        <v>6412557</v>
+        <v>6412532</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,17 +3225,13 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Bearbetat gran</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3356,42 +3356,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129528084</v>
+        <v>129527932</v>
       </c>
       <c r="B27" t="n">
-        <v>98724</v>
+        <v>92870</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3399,10 +3402,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569002</v>
+        <v>569016</v>
       </c>
       <c r="R27" t="n">
-        <v>6412837</v>
+        <v>6412795</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3568,45 +3571,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129527932</v>
+        <v>129528084</v>
       </c>
       <c r="B29" t="n">
-        <v>92870</v>
+        <v>98724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569016</v>
+        <v>569002</v>
       </c>
       <c r="R29" t="n">
-        <v>6412795</v>
+        <v>6412837</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3783,7 +3783,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129528031</v>
+        <v>129527952</v>
       </c>
       <c r="B31" t="n">
         <v>98724</v>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>568997</v>
+        <v>569027</v>
       </c>
       <c r="R31" t="n">
-        <v>6412845</v>
+        <v>6412813</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,7 +3889,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129527952</v>
+        <v>129528031</v>
       </c>
       <c r="B32" t="n">
         <v>98724</v>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569027</v>
+        <v>568997</v>
       </c>
       <c r="R32" t="n">
-        <v>6412813</v>
+        <v>6412845</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -1324,45 +1324,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129527859</v>
+        <v>129527942</v>
       </c>
       <c r="B8" t="n">
-        <v>92832</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1370,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569043</v>
+        <v>569019</v>
       </c>
       <c r="R8" t="n">
-        <v>6412642</v>
+        <v>6412827</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,42 +1430,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129527942</v>
+        <v>129527859</v>
       </c>
       <c r="B9" t="n">
-        <v>98724</v>
+        <v>92832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569019</v>
+        <v>569043</v>
       </c>
       <c r="R9" t="n">
-        <v>6412827</v>
+        <v>6412642</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129527700</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129527963</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129527842</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129527900</v>
+        <v>129527787</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,7 +1136,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1151,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569029</v>
+        <v>569153</v>
       </c>
       <c r="R6" t="n">
-        <v>6412790</v>
+        <v>6412439</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129527787</v>
+        <v>129527900</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,11 +1246,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569153</v>
+        <v>569029</v>
       </c>
       <c r="R7" t="n">
-        <v>6412439</v>
+        <v>6412790</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1327,7 @@
         <v>129527942</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>129527859</v>
       </c>
       <c r="B9" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>129528060</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129527924</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>129528042</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>129527714</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,42 +1963,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129527906</v>
+        <v>129527808</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569032</v>
+        <v>569157</v>
       </c>
       <c r="R14" t="n">
-        <v>6412788</v>
+        <v>6412484</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,13 +2044,17 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2069,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129527885</v>
+        <v>129527906</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2112,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568987</v>
+        <v>569032</v>
       </c>
       <c r="R15" t="n">
-        <v>6412775</v>
+        <v>6412788</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,42 +2179,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129527808</v>
+        <v>129527885</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2218,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569157</v>
+        <v>568987</v>
       </c>
       <c r="R16" t="n">
-        <v>6412484</v>
+        <v>6412775</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,17 +2260,13 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>129528013</v>
       </c>
       <c r="B17" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>129527636</v>
       </c>
       <c r="B18" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>129528074</v>
       </c>
       <c r="B19" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>129527910</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>129527766</v>
       </c>
       <c r="B21" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>129527872</v>
       </c>
       <c r="B22" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>129527753</v>
       </c>
       <c r="B25" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>129527675</v>
       </c>
       <c r="B26" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>129527932</v>
       </c>
       <c r="B27" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>129527981</v>
       </c>
       <c r="B28" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>129528084</v>
       </c>
       <c r="B29" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>129528002</v>
       </c>
       <c r="B30" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>129527952</v>
       </c>
       <c r="B31" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>129528031</v>
       </c>
       <c r="B32" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129527787</v>
+        <v>129527900</v>
       </c>
       <c r="B6" t="n">
         <v>98727</v>
@@ -1136,11 +1136,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1155,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569153</v>
+        <v>569029</v>
       </c>
       <c r="R6" t="n">
-        <v>6412439</v>
+        <v>6412790</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129527900</v>
+        <v>129527787</v>
       </c>
       <c r="B7" t="n">
         <v>98727</v>
@@ -1246,7 +1242,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569029</v>
+        <v>569153</v>
       </c>
       <c r="R7" t="n">
-        <v>6412790</v>
+        <v>6412439</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,42 +1324,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129527942</v>
+        <v>129527859</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>92835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569019</v>
+        <v>569043</v>
       </c>
       <c r="R8" t="n">
-        <v>6412827</v>
+        <v>6412642</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,45 +1433,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129527859</v>
+        <v>129527942</v>
       </c>
       <c r="B9" t="n">
-        <v>92835</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569043</v>
+        <v>569019</v>
       </c>
       <c r="R9" t="n">
-        <v>6412642</v>
+        <v>6412827</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129527924</v>
+        <v>129528042</v>
       </c>
       <c r="B11" t="n">
         <v>98727</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569016</v>
+        <v>568999</v>
       </c>
       <c r="R11" t="n">
-        <v>6412795</v>
+        <v>6412827</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129528042</v>
+        <v>129527714</v>
       </c>
       <c r="B12" t="n">
         <v>98727</v>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568999</v>
+        <v>569077</v>
       </c>
       <c r="R12" t="n">
-        <v>6412827</v>
+        <v>6412589</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129527714</v>
+        <v>129527924</v>
       </c>
       <c r="B13" t="n">
         <v>98727</v>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569077</v>
+        <v>569016</v>
       </c>
       <c r="R13" t="n">
-        <v>6412589</v>
+        <v>6412795</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129527906</v>
+        <v>129527885</v>
       </c>
       <c r="B15" t="n">
         <v>98727</v>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569032</v>
+        <v>568987</v>
       </c>
       <c r="R15" t="n">
-        <v>6412788</v>
+        <v>6412775</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129527885</v>
+        <v>129527906</v>
       </c>
       <c r="B16" t="n">
         <v>98727</v>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>568987</v>
+        <v>569032</v>
       </c>
       <c r="R16" t="n">
-        <v>6412775</v>
+        <v>6412788</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2933,27 +2933,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129527732</v>
+        <v>129528112</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>58097</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2964,11 +2964,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2976,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569083</v>
+        <v>569104</v>
       </c>
       <c r="R23" t="n">
-        <v>6412557</v>
+        <v>6412595</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,11 +3008,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Bearbetat gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,27 +3034,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129528112</v>
+        <v>129527732</v>
       </c>
       <c r="B24" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3074,7 +3065,11 @@
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3082,10 +3077,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569104</v>
+        <v>569083</v>
       </c>
       <c r="R24" t="n">
-        <v>6412595</v>
+        <v>6412557</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3118,6 +3113,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3144,7 +3144,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129527753</v>
+        <v>129527675</v>
       </c>
       <c r="B25" t="n">
         <v>98727</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569077</v>
+        <v>569104</v>
       </c>
       <c r="R25" t="n">
-        <v>6412532</v>
+        <v>6412595</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129527675</v>
+        <v>129527753</v>
       </c>
       <c r="B26" t="n">
         <v>98727</v>
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569104</v>
+        <v>569077</v>
       </c>
       <c r="R26" t="n">
-        <v>6412595</v>
+        <v>6412532</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129527981</v>
+        <v>129528084</v>
       </c>
       <c r="B28" t="n">
         <v>98727</v>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569004</v>
+        <v>569002</v>
       </c>
       <c r="R28" t="n">
-        <v>6412822</v>
+        <v>6412837</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129528084</v>
+        <v>129527981</v>
       </c>
       <c r="B29" t="n">
         <v>98727</v>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569002</v>
+        <v>569004</v>
       </c>
       <c r="R29" t="n">
-        <v>6412837</v>
+        <v>6412822</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3783,7 +3783,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129527952</v>
+        <v>129528031</v>
       </c>
       <c r="B31" t="n">
         <v>98727</v>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569027</v>
+        <v>568997</v>
       </c>
       <c r="R31" t="n">
-        <v>6412813</v>
+        <v>6412845</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,7 +3889,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129528031</v>
+        <v>129527952</v>
       </c>
       <c r="B32" t="n">
         <v>98727</v>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>568997</v>
+        <v>569027</v>
       </c>
       <c r="R32" t="n">
-        <v>6412845</v>
+        <v>6412813</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -1645,7 +1645,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129528042</v>
+        <v>129527714</v>
       </c>
       <c r="B11" t="n">
         <v>98727</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568999</v>
+        <v>569077</v>
       </c>
       <c r="R11" t="n">
-        <v>6412827</v>
+        <v>6412589</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129527714</v>
+        <v>129528042</v>
       </c>
       <c r="B12" t="n">
         <v>98727</v>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569077</v>
+        <v>568999</v>
       </c>
       <c r="R12" t="n">
-        <v>6412589</v>
+        <v>6412827</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129527885</v>
+        <v>129527906</v>
       </c>
       <c r="B15" t="n">
         <v>98727</v>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568987</v>
+        <v>569032</v>
       </c>
       <c r="R15" t="n">
-        <v>6412775</v>
+        <v>6412788</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129527906</v>
+        <v>129527885</v>
       </c>
       <c r="B16" t="n">
         <v>98727</v>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569032</v>
+        <v>568987</v>
       </c>
       <c r="R16" t="n">
-        <v>6412788</v>
+        <v>6412775</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2933,27 +2933,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129528112</v>
+        <v>129527732</v>
       </c>
       <c r="B23" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2964,7 +2964,11 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2972,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569104</v>
+        <v>569083</v>
       </c>
       <c r="R23" t="n">
-        <v>6412595</v>
+        <v>6412557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3008,6 +3012,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3034,27 +3043,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129527732</v>
+        <v>129528112</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>58097</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3065,11 +3074,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3077,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569083</v>
+        <v>569104</v>
       </c>
       <c r="R24" t="n">
-        <v>6412557</v>
+        <v>6412595</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,11 +3118,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bearbetat gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3144,7 +3144,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129527675</v>
+        <v>129527753</v>
       </c>
       <c r="B25" t="n">
         <v>98727</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569104</v>
+        <v>569077</v>
       </c>
       <c r="R25" t="n">
-        <v>6412595</v>
+        <v>6412532</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129527753</v>
+        <v>129527675</v>
       </c>
       <c r="B26" t="n">
         <v>98727</v>
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569077</v>
+        <v>569104</v>
       </c>
       <c r="R26" t="n">
-        <v>6412532</v>
+        <v>6412595</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129528084</v>
+        <v>129527981</v>
       </c>
       <c r="B28" t="n">
         <v>98727</v>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569002</v>
+        <v>569004</v>
       </c>
       <c r="R28" t="n">
-        <v>6412837</v>
+        <v>6412822</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129527981</v>
+        <v>129528084</v>
       </c>
       <c r="B29" t="n">
         <v>98727</v>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569004</v>
+        <v>569002</v>
       </c>
       <c r="R29" t="n">
-        <v>6412822</v>
+        <v>6412837</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -1324,45 +1324,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129527859</v>
+        <v>129527942</v>
       </c>
       <c r="B8" t="n">
-        <v>92835</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1370,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569043</v>
+        <v>569019</v>
       </c>
       <c r="R8" t="n">
-        <v>6412642</v>
+        <v>6412827</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,42 +1430,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129527942</v>
+        <v>129527859</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569019</v>
+        <v>569043</v>
       </c>
       <c r="R9" t="n">
-        <v>6412827</v>
+        <v>6412642</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129527714</v>
+        <v>129527924</v>
       </c>
       <c r="B11" t="n">
         <v>98727</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569077</v>
+        <v>569016</v>
       </c>
       <c r="R11" t="n">
-        <v>6412589</v>
+        <v>6412795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129527924</v>
+        <v>129527714</v>
       </c>
       <c r="B13" t="n">
         <v>98727</v>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569016</v>
+        <v>569077</v>
       </c>
       <c r="R13" t="n">
-        <v>6412795</v>
+        <v>6412589</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3043,38 +3043,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129528112</v>
+        <v>129527753</v>
       </c>
       <c r="B24" t="n">
-        <v>58097</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3082,10 +3086,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569104</v>
+        <v>569077</v>
       </c>
       <c r="R24" t="n">
-        <v>6412595</v>
+        <v>6412532</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3126,6 +3130,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3144,7 +3149,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129527753</v>
+        <v>129527675</v>
       </c>
       <c r="B25" t="n">
         <v>98727</v>
@@ -3187,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569077</v>
+        <v>569104</v>
       </c>
       <c r="R25" t="n">
-        <v>6412532</v>
+        <v>6412595</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3250,42 +3255,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129527675</v>
+        <v>129528112</v>
       </c>
       <c r="B26" t="n">
-        <v>98727</v>
+        <v>58097</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3337,7 +3338,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3783,7 +3783,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129528031</v>
+        <v>129527952</v>
       </c>
       <c r="B31" t="n">
         <v>98727</v>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>568997</v>
+        <v>569027</v>
       </c>
       <c r="R31" t="n">
-        <v>6412845</v>
+        <v>6412813</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,7 +3889,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129527952</v>
+        <v>129528031</v>
       </c>
       <c r="B32" t="n">
         <v>98727</v>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569027</v>
+        <v>568997</v>
       </c>
       <c r="R32" t="n">
-        <v>6412813</v>
+        <v>6412845</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -1324,42 +1324,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129527942</v>
+        <v>129527859</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>92835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569019</v>
+        <v>569043</v>
       </c>
       <c r="R8" t="n">
-        <v>6412827</v>
+        <v>6412642</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,45 +1433,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129527859</v>
+        <v>129527942</v>
       </c>
       <c r="B9" t="n">
-        <v>92835</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569043</v>
+        <v>569019</v>
       </c>
       <c r="R9" t="n">
-        <v>6412642</v>
+        <v>6412827</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129527924</v>
+        <v>129528042</v>
       </c>
       <c r="B11" t="n">
         <v>98727</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569016</v>
+        <v>568999</v>
       </c>
       <c r="R11" t="n">
-        <v>6412795</v>
+        <v>6412827</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129528042</v>
+        <v>129527714</v>
       </c>
       <c r="B12" t="n">
         <v>98727</v>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568999</v>
+        <v>569077</v>
       </c>
       <c r="R12" t="n">
-        <v>6412827</v>
+        <v>6412589</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129527714</v>
+        <v>129527924</v>
       </c>
       <c r="B13" t="n">
         <v>98727</v>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569077</v>
+        <v>569016</v>
       </c>
       <c r="R13" t="n">
-        <v>6412589</v>
+        <v>6412795</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2933,42 +2933,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129527732</v>
+        <v>129527753</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569083</v>
+        <v>569077</v>
       </c>
       <c r="R23" t="n">
-        <v>6412557</v>
+        <v>6412532</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,17 +3014,13 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Bearbetat gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3043,7 +3039,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129527753</v>
+        <v>129527675</v>
       </c>
       <c r="B24" t="n">
         <v>98727</v>
@@ -3086,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569077</v>
+        <v>569104</v>
       </c>
       <c r="R24" t="n">
-        <v>6412532</v>
+        <v>6412595</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,42 +3145,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129527675</v>
+        <v>129528112</v>
       </c>
       <c r="B25" t="n">
-        <v>98727</v>
+        <v>58097</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3236,7 +3228,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3255,27 +3246,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129528112</v>
+        <v>129527732</v>
       </c>
       <c r="B26" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3286,7 +3277,11 @@
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3294,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569104</v>
+        <v>569083</v>
       </c>
       <c r="R26" t="n">
-        <v>6412595</v>
+        <v>6412557</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,6 +3325,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3465,7 +3465,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129527981</v>
+        <v>129528084</v>
       </c>
       <c r="B28" t="n">
         <v>98727</v>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569004</v>
+        <v>569002</v>
       </c>
       <c r="R28" t="n">
-        <v>6412822</v>
+        <v>6412837</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129528084</v>
+        <v>129528002</v>
       </c>
       <c r="B29" t="n">
         <v>98727</v>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569002</v>
+        <v>569016</v>
       </c>
       <c r="R29" t="n">
-        <v>6412837</v>
+        <v>6412840</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129528002</v>
+        <v>129527981</v>
       </c>
       <c r="B30" t="n">
         <v>98727</v>
@@ -3720,10 +3720,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569016</v>
+        <v>569004</v>
       </c>
       <c r="R30" t="n">
-        <v>6412840</v>
+        <v>6412822</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,7 +3783,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129527952</v>
+        <v>129528031</v>
       </c>
       <c r="B31" t="n">
         <v>98727</v>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569027</v>
+        <v>568997</v>
       </c>
       <c r="R31" t="n">
-        <v>6412813</v>
+        <v>6412845</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,7 +3889,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129528031</v>
+        <v>129527952</v>
       </c>
       <c r="B32" t="n">
         <v>98727</v>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>568997</v>
+        <v>569027</v>
       </c>
       <c r="R32" t="n">
-        <v>6412845</v>
+        <v>6412813</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -1645,7 +1645,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129528042</v>
+        <v>129527924</v>
       </c>
       <c r="B11" t="n">
         <v>98727</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568999</v>
+        <v>569016</v>
       </c>
       <c r="R11" t="n">
-        <v>6412827</v>
+        <v>6412795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129527714</v>
+        <v>129528042</v>
       </c>
       <c r="B12" t="n">
         <v>98727</v>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569077</v>
+        <v>568999</v>
       </c>
       <c r="R12" t="n">
-        <v>6412589</v>
+        <v>6412827</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129527924</v>
+        <v>129527714</v>
       </c>
       <c r="B13" t="n">
         <v>98727</v>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569016</v>
+        <v>569077</v>
       </c>
       <c r="R13" t="n">
-        <v>6412795</v>
+        <v>6412589</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2933,42 +2933,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129527753</v>
+        <v>129528112</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>58097</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2976,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569077</v>
+        <v>569104</v>
       </c>
       <c r="R23" t="n">
-        <v>6412532</v>
+        <v>6412595</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3016,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3039,42 +3034,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129527675</v>
+        <v>129527732</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3082,10 +3077,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569104</v>
+        <v>569083</v>
       </c>
       <c r="R24" t="n">
-        <v>6412595</v>
+        <v>6412557</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,13 +3115,17 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3145,38 +3144,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129528112</v>
+        <v>129527753</v>
       </c>
       <c r="B25" t="n">
-        <v>58097</v>
+        <v>98727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3184,10 +3187,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569104</v>
+        <v>569077</v>
       </c>
       <c r="R25" t="n">
-        <v>6412595</v>
+        <v>6412532</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,6 +3231,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3246,42 +3250,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129527732</v>
+        <v>129527675</v>
       </c>
       <c r="B26" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3289,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569083</v>
+        <v>569104</v>
       </c>
       <c r="R26" t="n">
-        <v>6412557</v>
+        <v>6412595</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3327,17 +3331,13 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Bearbetat gran</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129528084</v>
+        <v>129527981</v>
       </c>
       <c r="B28" t="n">
         <v>98727</v>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569002</v>
+        <v>569004</v>
       </c>
       <c r="R28" t="n">
-        <v>6412837</v>
+        <v>6412822</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129528002</v>
+        <v>129528084</v>
       </c>
       <c r="B29" t="n">
         <v>98727</v>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569016</v>
+        <v>569002</v>
       </c>
       <c r="R29" t="n">
-        <v>6412840</v>
+        <v>6412837</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129527981</v>
+        <v>129528002</v>
       </c>
       <c r="B30" t="n">
         <v>98727</v>
@@ -3720,10 +3720,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569004</v>
+        <v>569016</v>
       </c>
       <c r="R30" t="n">
-        <v>6412822</v>
+        <v>6412840</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,7 +3783,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129528031</v>
+        <v>129527952</v>
       </c>
       <c r="B31" t="n">
         <v>98727</v>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>568997</v>
+        <v>569027</v>
       </c>
       <c r="R31" t="n">
-        <v>6412845</v>
+        <v>6412813</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,7 +3889,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129527952</v>
+        <v>129528031</v>
       </c>
       <c r="B32" t="n">
         <v>98727</v>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569027</v>
+        <v>568997</v>
       </c>
       <c r="R32" t="n">
-        <v>6412813</v>
+        <v>6412845</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129527700</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129527963</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129527842</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129527900</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129527787</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>129527859</v>
       </c>
       <c r="B8" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>129527942</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>129528060</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129527924</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>129528042</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>129527714</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>129527808</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>129527906</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>129527885</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129528013</v>
       </c>
       <c r="B17" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>129527636</v>
       </c>
       <c r="B18" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>129528074</v>
       </c>
       <c r="B19" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>129527910</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>129527766</v>
       </c>
       <c r="B21" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>129527872</v>
       </c>
       <c r="B22" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,27 +2933,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129528112</v>
+        <v>129527732</v>
       </c>
       <c r="B23" t="n">
-        <v>58097</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2964,7 +2964,11 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2972,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569104</v>
+        <v>569083</v>
       </c>
       <c r="R23" t="n">
-        <v>6412595</v>
+        <v>6412557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3008,6 +3012,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3034,27 +3043,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129527732</v>
+        <v>129528112</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>58100</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3065,11 +3074,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3077,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569083</v>
+        <v>569104</v>
       </c>
       <c r="R24" t="n">
-        <v>6412557</v>
+        <v>6412595</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,11 +3118,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bearbetat gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3147,7 +3147,7 @@
         <v>129527753</v>
       </c>
       <c r="B25" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>129527675</v>
       </c>
       <c r="B26" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>129527932</v>
       </c>
       <c r="B27" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>129527981</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>129528084</v>
       </c>
       <c r="B29" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>129528002</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>129527952</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>129528031</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>129527594</v>
       </c>
       <c r="B33" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -2933,27 +2933,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129527732</v>
+        <v>129528112</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>58100</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2964,11 +2964,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2976,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569083</v>
+        <v>569104</v>
       </c>
       <c r="R23" t="n">
-        <v>6412557</v>
+        <v>6412595</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,11 +3008,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Bearbetat gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,38 +3034,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129528112</v>
+        <v>129527753</v>
       </c>
       <c r="B24" t="n">
-        <v>58100</v>
+        <v>98756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3082,10 +3077,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569104</v>
+        <v>569077</v>
       </c>
       <c r="R24" t="n">
-        <v>6412595</v>
+        <v>6412532</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3126,6 +3121,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3144,7 +3140,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129527753</v>
+        <v>129527675</v>
       </c>
       <c r="B25" t="n">
         <v>98756</v>
@@ -3187,10 +3183,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569077</v>
+        <v>569104</v>
       </c>
       <c r="R25" t="n">
-        <v>6412532</v>
+        <v>6412595</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3250,42 +3246,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129527675</v>
+        <v>129527732</v>
       </c>
       <c r="B26" t="n">
-        <v>98756</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3293,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569104</v>
+        <v>569083</v>
       </c>
       <c r="R26" t="n">
-        <v>6412595</v>
+        <v>6412557</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3331,13 +3327,17 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129527700</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129527963</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129527842</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129527900</v>
+        <v>129527787</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,7 +1136,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1151,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569029</v>
+        <v>569153</v>
       </c>
       <c r="R6" t="n">
-        <v>6412790</v>
+        <v>6412439</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129527787</v>
+        <v>129527900</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,11 +1246,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569153</v>
+        <v>569029</v>
       </c>
       <c r="R7" t="n">
-        <v>6412439</v>
+        <v>6412790</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,45 +1324,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129527859</v>
+        <v>129527942</v>
       </c>
       <c r="B8" t="n">
-        <v>92863</v>
+        <v>98768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1370,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569043</v>
+        <v>569019</v>
       </c>
       <c r="R8" t="n">
-        <v>6412642</v>
+        <v>6412827</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,42 +1430,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129527942</v>
+        <v>129527859</v>
       </c>
       <c r="B9" t="n">
-        <v>98756</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569019</v>
+        <v>569043</v>
       </c>
       <c r="R9" t="n">
-        <v>6412827</v>
+        <v>6412642</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
         <v>129528060</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129527924</v>
+        <v>129527714</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569016</v>
+        <v>569077</v>
       </c>
       <c r="R11" t="n">
-        <v>6412795</v>
+        <v>6412589</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1754,7 +1754,7 @@
         <v>129528042</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129527714</v>
+        <v>129527924</v>
       </c>
       <c r="B13" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569077</v>
+        <v>569016</v>
       </c>
       <c r="R13" t="n">
-        <v>6412589</v>
+        <v>6412795</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
         <v>129527808</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129527906</v>
+        <v>129527885</v>
       </c>
       <c r="B15" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569032</v>
+        <v>568987</v>
       </c>
       <c r="R15" t="n">
-        <v>6412788</v>
+        <v>6412775</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129527885</v>
+        <v>129527906</v>
       </c>
       <c r="B16" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>568987</v>
+        <v>569032</v>
       </c>
       <c r="R16" t="n">
-        <v>6412775</v>
+        <v>6412788</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2288,7 +2288,7 @@
         <v>129528013</v>
       </c>
       <c r="B17" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>129527636</v>
       </c>
       <c r="B18" t="n">
-        <v>92234</v>
+        <v>92240</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>129528074</v>
       </c>
       <c r="B19" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>129527910</v>
       </c>
       <c r="B20" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>129527766</v>
       </c>
       <c r="B21" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>129527872</v>
       </c>
       <c r="B22" t="n">
-        <v>92234</v>
+        <v>92240</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,27 +2933,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129528112</v>
+        <v>129527732</v>
       </c>
       <c r="B23" t="n">
-        <v>58100</v>
+        <v>57732</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2964,7 +2964,11 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2972,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569104</v>
+        <v>569083</v>
       </c>
       <c r="R23" t="n">
-        <v>6412595</v>
+        <v>6412557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3008,6 +3012,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3034,42 +3043,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129527753</v>
+        <v>129528112</v>
       </c>
       <c r="B24" t="n">
-        <v>98756</v>
+        <v>58105</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3077,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569077</v>
+        <v>569104</v>
       </c>
       <c r="R24" t="n">
-        <v>6412532</v>
+        <v>6412595</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,7 +3126,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3140,10 +3144,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129527675</v>
+        <v>129527753</v>
       </c>
       <c r="B25" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3183,10 +3187,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569104</v>
+        <v>569077</v>
       </c>
       <c r="R25" t="n">
-        <v>6412595</v>
+        <v>6412532</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3246,42 +3250,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129527732</v>
+        <v>129527675</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>98768</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3289,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569083</v>
+        <v>569104</v>
       </c>
       <c r="R26" t="n">
-        <v>6412557</v>
+        <v>6412595</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3327,17 +3331,13 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Bearbetat gran</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>129527932</v>
       </c>
       <c r="B27" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>129527981</v>
       </c>
       <c r="B28" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3571,10 +3571,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129528084</v>
+        <v>129528002</v>
       </c>
       <c r="B29" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569002</v>
+        <v>569016</v>
       </c>
       <c r="R29" t="n">
-        <v>6412837</v>
+        <v>6412840</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129528002</v>
+        <v>129528084</v>
       </c>
       <c r="B30" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,10 +3720,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569016</v>
+        <v>569002</v>
       </c>
       <c r="R30" t="n">
-        <v>6412840</v>
+        <v>6412837</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,10 +3783,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129527952</v>
+        <v>129528031</v>
       </c>
       <c r="B31" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569027</v>
+        <v>568997</v>
       </c>
       <c r="R31" t="n">
-        <v>6412813</v>
+        <v>6412845</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,10 +3889,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129528031</v>
+        <v>129527952</v>
       </c>
       <c r="B32" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>568997</v>
+        <v>569027</v>
       </c>
       <c r="R32" t="n">
-        <v>6412845</v>
+        <v>6412813</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3998,7 +3998,7 @@
         <v>129527594</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129527700</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129527963</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129527842</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129527787</v>
+        <v>129527900</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,11 +1136,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1155,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569153</v>
+        <v>569029</v>
       </c>
       <c r="R6" t="n">
-        <v>6412439</v>
+        <v>6412790</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129527900</v>
+        <v>129527787</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,7 +1242,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569029</v>
+        <v>569153</v>
       </c>
       <c r="R7" t="n">
-        <v>6412790</v>
+        <v>6412439</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,42 +1324,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129527942</v>
+        <v>129527859</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>92870</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569019</v>
+        <v>569043</v>
       </c>
       <c r="R8" t="n">
-        <v>6412827</v>
+        <v>6412642</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,45 +1433,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129527859</v>
+        <v>129527942</v>
       </c>
       <c r="B9" t="n">
-        <v>92869</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569043</v>
+        <v>569019</v>
       </c>
       <c r="R9" t="n">
-        <v>6412642</v>
+        <v>6412827</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
         <v>129528060</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129527714</v>
+        <v>129527924</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569077</v>
+        <v>569016</v>
       </c>
       <c r="R11" t="n">
-        <v>6412589</v>
+        <v>6412795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1754,7 +1754,7 @@
         <v>129528042</v>
       </c>
       <c r="B12" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129527924</v>
+        <v>129527714</v>
       </c>
       <c r="B13" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569016</v>
+        <v>569077</v>
       </c>
       <c r="R13" t="n">
-        <v>6412795</v>
+        <v>6412589</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
         <v>129527808</v>
       </c>
       <c r="B14" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129527885</v>
+        <v>129527906</v>
       </c>
       <c r="B15" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568987</v>
+        <v>569032</v>
       </c>
       <c r="R15" t="n">
-        <v>6412775</v>
+        <v>6412788</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129527906</v>
+        <v>129527885</v>
       </c>
       <c r="B16" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569032</v>
+        <v>568987</v>
       </c>
       <c r="R16" t="n">
-        <v>6412788</v>
+        <v>6412775</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2288,7 +2288,7 @@
         <v>129528013</v>
       </c>
       <c r="B17" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>129527636</v>
       </c>
       <c r="B18" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>129528074</v>
       </c>
       <c r="B19" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>129527910</v>
       </c>
       <c r="B20" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>129527766</v>
       </c>
       <c r="B21" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>129527872</v>
       </c>
       <c r="B22" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,42 +2933,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129527732</v>
+        <v>129527753</v>
       </c>
       <c r="B23" t="n">
-        <v>57732</v>
+        <v>98769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569083</v>
+        <v>569077</v>
       </c>
       <c r="R23" t="n">
-        <v>6412557</v>
+        <v>6412532</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,17 +3014,13 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Bearbetat gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3043,38 +3039,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129528112</v>
+        <v>129527675</v>
       </c>
       <c r="B24" t="n">
-        <v>58105</v>
+        <v>98769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3126,6 +3126,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3144,42 +3145,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129527753</v>
+        <v>129527732</v>
       </c>
       <c r="B25" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3187,10 +3188,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569077</v>
+        <v>569083</v>
       </c>
       <c r="R25" t="n">
-        <v>6412532</v>
+        <v>6412557</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3225,13 +3226,17 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3250,42 +3255,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129527675</v>
+        <v>129528112</v>
       </c>
       <c r="B26" t="n">
-        <v>98768</v>
+        <v>58106</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3337,7 +3338,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>129527932</v>
       </c>
       <c r="B27" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>129527981</v>
       </c>
       <c r="B28" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3571,10 +3571,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129528002</v>
+        <v>129528084</v>
       </c>
       <c r="B29" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569016</v>
+        <v>569002</v>
       </c>
       <c r="R29" t="n">
-        <v>6412840</v>
+        <v>6412837</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129528084</v>
+        <v>129528002</v>
       </c>
       <c r="B30" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,10 +3720,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569002</v>
+        <v>569016</v>
       </c>
       <c r="R30" t="n">
-        <v>6412837</v>
+        <v>6412840</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,10 +3783,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129528031</v>
+        <v>129527952</v>
       </c>
       <c r="B31" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>568997</v>
+        <v>569027</v>
       </c>
       <c r="R31" t="n">
-        <v>6412845</v>
+        <v>6412813</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,10 +3889,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129527952</v>
+        <v>129528031</v>
       </c>
       <c r="B32" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569027</v>
+        <v>568997</v>
       </c>
       <c r="R32" t="n">
-        <v>6412813</v>
+        <v>6412845</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3998,7 +3998,7 @@
         <v>129527594</v>
       </c>
       <c r="B33" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -3356,45 +3356,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129527932</v>
+        <v>129527981</v>
       </c>
       <c r="B27" t="n">
-        <v>92908</v>
+        <v>98769</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3402,10 +3399,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569016</v>
+        <v>569004</v>
       </c>
       <c r="R27" t="n">
-        <v>6412795</v>
+        <v>6412822</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3465,7 +3462,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129527981</v>
+        <v>129528084</v>
       </c>
       <c r="B28" t="n">
         <v>98769</v>
@@ -3508,10 +3505,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569004</v>
+        <v>569002</v>
       </c>
       <c r="R28" t="n">
-        <v>6412822</v>
+        <v>6412837</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,7 +3568,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129528084</v>
+        <v>129528002</v>
       </c>
       <c r="B29" t="n">
         <v>98769</v>
@@ -3614,10 +3611,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569002</v>
+        <v>569016</v>
       </c>
       <c r="R29" t="n">
-        <v>6412837</v>
+        <v>6412840</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3677,42 +3674,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129528002</v>
+        <v>129527932</v>
       </c>
       <c r="B30" t="n">
-        <v>98769</v>
+        <v>92908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>569016</v>
       </c>
       <c r="R30" t="n">
-        <v>6412840</v>
+        <v>6412795</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129527700</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129527963</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129527842</v>
       </c>
       <c r="B5" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129527900</v>
       </c>
       <c r="B6" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129527787</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>129527859</v>
       </c>
       <c r="B8" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>129527942</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>129528060</v>
       </c>
       <c r="B10" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129527924</v>
       </c>
       <c r="B11" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>129528042</v>
       </c>
       <c r="B12" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>129527714</v>
       </c>
       <c r="B13" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>129527906</v>
       </c>
       <c r="B15" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>129527885</v>
       </c>
       <c r="B16" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129528013</v>
       </c>
       <c r="B17" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>129527636</v>
       </c>
       <c r="B18" t="n">
-        <v>92241</v>
+        <v>92246</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>129528074</v>
       </c>
       <c r="B19" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>129527910</v>
       </c>
       <c r="B20" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>129527766</v>
       </c>
       <c r="B21" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>129527872</v>
       </c>
       <c r="B22" t="n">
-        <v>92241</v>
+        <v>92246</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,42 +2933,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129527753</v>
+        <v>129528112</v>
       </c>
       <c r="B23" t="n">
-        <v>98769</v>
+        <v>58106</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2976,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569077</v>
+        <v>569104</v>
       </c>
       <c r="R23" t="n">
-        <v>6412532</v>
+        <v>6412595</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3016,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3039,42 +3034,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129527675</v>
+        <v>129527732</v>
       </c>
       <c r="B24" t="n">
-        <v>98769</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3082,10 +3077,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569104</v>
+        <v>569083</v>
       </c>
       <c r="R24" t="n">
-        <v>6412595</v>
+        <v>6412557</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,13 +3115,17 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3145,42 +3144,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129527732</v>
+        <v>129527753</v>
       </c>
       <c r="B25" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3188,10 +3187,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569083</v>
+        <v>569077</v>
       </c>
       <c r="R25" t="n">
-        <v>6412557</v>
+        <v>6412532</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3226,17 +3225,13 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Bearbetat gran</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3255,38 +3250,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129528112</v>
+        <v>129527675</v>
       </c>
       <c r="B26" t="n">
-        <v>58106</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3338,6 +3337,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>129527981</v>
       </c>
       <c r="B27" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>129528084</v>
       </c>
       <c r="B28" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>129528002</v>
       </c>
       <c r="B29" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>129527932</v>
       </c>
       <c r="B30" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>129527952</v>
       </c>
       <c r="B31" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>129528031</v>
       </c>
       <c r="B32" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -1324,45 +1324,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129527859</v>
+        <v>129527942</v>
       </c>
       <c r="B8" t="n">
-        <v>92875</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1370,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569043</v>
+        <v>569019</v>
       </c>
       <c r="R8" t="n">
-        <v>6412642</v>
+        <v>6412827</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,42 +1430,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129527942</v>
+        <v>129527859</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>92875</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569019</v>
+        <v>569043</v>
       </c>
       <c r="R9" t="n">
-        <v>6412827</v>
+        <v>6412642</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1963,42 +1963,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129527808</v>
+        <v>129527906</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569157</v>
+        <v>569032</v>
       </c>
       <c r="R14" t="n">
-        <v>6412484</v>
+        <v>6412788</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,17 +2044,13 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2073,7 +2069,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129527906</v>
+        <v>129527885</v>
       </c>
       <c r="B15" t="n">
         <v>98774</v>
@@ -2116,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569032</v>
+        <v>568987</v>
       </c>
       <c r="R15" t="n">
-        <v>6412788</v>
+        <v>6412775</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,42 +2175,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129527885</v>
+        <v>129527808</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2222,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>568987</v>
+        <v>569157</v>
       </c>
       <c r="R16" t="n">
-        <v>6412775</v>
+        <v>6412484</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,13 +2256,17 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2933,27 +2933,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129528112</v>
+        <v>129527732</v>
       </c>
       <c r="B23" t="n">
-        <v>58106</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2964,7 +2964,11 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2972,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569104</v>
+        <v>569083</v>
       </c>
       <c r="R23" t="n">
-        <v>6412595</v>
+        <v>6412557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3008,6 +3012,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3034,42 +3043,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129527732</v>
+        <v>129527753</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3077,10 +3086,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569083</v>
+        <v>569077</v>
       </c>
       <c r="R24" t="n">
-        <v>6412557</v>
+        <v>6412532</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3115,17 +3124,13 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bearbetat gran</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3144,42 +3149,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129527753</v>
+        <v>129528112</v>
       </c>
       <c r="B25" t="n">
-        <v>98774</v>
+        <v>58106</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3187,10 +3188,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569077</v>
+        <v>569104</v>
       </c>
       <c r="R25" t="n">
-        <v>6412532</v>
+        <v>6412595</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,7 +3232,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3356,42 +3356,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129527981</v>
+        <v>129527932</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>92913</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3399,10 +3402,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569004</v>
+        <v>569016</v>
       </c>
       <c r="R27" t="n">
-        <v>6412822</v>
+        <v>6412795</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3568,7 +3571,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129528002</v>
+        <v>129527981</v>
       </c>
       <c r="B29" t="n">
         <v>98774</v>
@@ -3611,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569016</v>
+        <v>569004</v>
       </c>
       <c r="R29" t="n">
-        <v>6412840</v>
+        <v>6412822</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3674,45 +3677,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129527932</v>
+        <v>129528002</v>
       </c>
       <c r="B30" t="n">
-        <v>92913</v>
+        <v>98774</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>569016</v>
       </c>
       <c r="R30" t="n">
-        <v>6412795</v>
+        <v>6412840</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,7 +3783,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129527952</v>
+        <v>129528031</v>
       </c>
       <c r="B31" t="n">
         <v>98774</v>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569027</v>
+        <v>568997</v>
       </c>
       <c r="R31" t="n">
-        <v>6412813</v>
+        <v>6412845</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,7 +3889,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129528031</v>
+        <v>129527952</v>
       </c>
       <c r="B32" t="n">
         <v>98774</v>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>568997</v>
+        <v>569027</v>
       </c>
       <c r="R32" t="n">
-        <v>6412845</v>
+        <v>6412813</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -1324,42 +1324,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129527942</v>
+        <v>129527859</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>92875</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569019</v>
+        <v>569043</v>
       </c>
       <c r="R8" t="n">
-        <v>6412827</v>
+        <v>6412642</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,45 +1433,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129527859</v>
+        <v>129527942</v>
       </c>
       <c r="B9" t="n">
-        <v>92875</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569043</v>
+        <v>569019</v>
       </c>
       <c r="R9" t="n">
-        <v>6412642</v>
+        <v>6412827</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1963,42 +1963,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129527906</v>
+        <v>129527808</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569032</v>
+        <v>569157</v>
       </c>
       <c r="R14" t="n">
-        <v>6412788</v>
+        <v>6412484</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,13 +2044,17 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2175,42 +2179,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129527808</v>
+        <v>129527906</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2218,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569157</v>
+        <v>569032</v>
       </c>
       <c r="R16" t="n">
-        <v>6412484</v>
+        <v>6412788</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,17 +2260,13 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -3043,42 +3043,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129527753</v>
+        <v>129528112</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>58106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3086,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569077</v>
+        <v>569104</v>
       </c>
       <c r="R24" t="n">
-        <v>6412532</v>
+        <v>6412595</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,7 +3126,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3149,38 +3144,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129528112</v>
+        <v>129527675</v>
       </c>
       <c r="B25" t="n">
-        <v>58106</v>
+        <v>98774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3232,6 +3231,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129527675</v>
+        <v>129527753</v>
       </c>
       <c r="B26" t="n">
         <v>98774</v>
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569104</v>
+        <v>569077</v>
       </c>
       <c r="R26" t="n">
-        <v>6412595</v>
+        <v>6412532</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3783,7 +3783,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129528031</v>
+        <v>129527952</v>
       </c>
       <c r="B31" t="n">
         <v>98774</v>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>568997</v>
+        <v>569027</v>
       </c>
       <c r="R31" t="n">
-        <v>6412845</v>
+        <v>6412813</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,7 +3889,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129527952</v>
+        <v>129528031</v>
       </c>
       <c r="B32" t="n">
         <v>98774</v>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569027</v>
+        <v>568997</v>
       </c>
       <c r="R32" t="n">
-        <v>6412813</v>
+        <v>6412845</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -2073,7 +2073,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129527885</v>
+        <v>129527906</v>
       </c>
       <c r="B15" t="n">
         <v>98774</v>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568987</v>
+        <v>569032</v>
       </c>
       <c r="R15" t="n">
-        <v>6412775</v>
+        <v>6412788</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129527906</v>
+        <v>129527885</v>
       </c>
       <c r="B16" t="n">
         <v>98774</v>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569032</v>
+        <v>568987</v>
       </c>
       <c r="R16" t="n">
-        <v>6412788</v>
+        <v>6412775</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2933,27 +2933,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129527732</v>
+        <v>129528112</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>58106</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2964,11 +2964,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2976,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569083</v>
+        <v>569104</v>
       </c>
       <c r="R23" t="n">
-        <v>6412557</v>
+        <v>6412595</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,11 +3008,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Bearbetat gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,38 +3034,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129528112</v>
+        <v>129527753</v>
       </c>
       <c r="B24" t="n">
-        <v>58106</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3082,10 +3077,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569104</v>
+        <v>569077</v>
       </c>
       <c r="R24" t="n">
-        <v>6412595</v>
+        <v>6412532</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3126,6 +3121,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3250,42 +3246,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129527753</v>
+        <v>129527732</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3293,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569077</v>
+        <v>569083</v>
       </c>
       <c r="R26" t="n">
-        <v>6412532</v>
+        <v>6412557</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3331,13 +3327,17 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129528084</v>
+        <v>129527981</v>
       </c>
       <c r="B28" t="n">
         <v>98774</v>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569002</v>
+        <v>569004</v>
       </c>
       <c r="R28" t="n">
-        <v>6412837</v>
+        <v>6412822</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129527981</v>
+        <v>129528084</v>
       </c>
       <c r="B29" t="n">
         <v>98774</v>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569004</v>
+        <v>569002</v>
       </c>
       <c r="R29" t="n">
-        <v>6412822</v>
+        <v>6412837</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129527700</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129527963</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129527842</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129527900</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129527787</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>129527859</v>
       </c>
       <c r="B8" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>129527942</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>129528060</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129527924</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>129528042</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>129527714</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>129527906</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>129527885</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129528013</v>
       </c>
       <c r="B17" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>129527636</v>
       </c>
       <c r="B18" t="n">
-        <v>92246</v>
+        <v>92250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>129528074</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>129527910</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>129527766</v>
       </c>
       <c r="B21" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>129527872</v>
       </c>
       <c r="B22" t="n">
-        <v>92246</v>
+        <v>92250</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,27 +2933,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129528112</v>
+        <v>129527732</v>
       </c>
       <c r="B23" t="n">
-        <v>58106</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2964,7 +2964,11 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2972,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569104</v>
+        <v>569083</v>
       </c>
       <c r="R23" t="n">
-        <v>6412595</v>
+        <v>6412557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3008,6 +3012,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3034,42 +3043,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129527753</v>
+        <v>129528112</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>58106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3077,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569077</v>
+        <v>569104</v>
       </c>
       <c r="R24" t="n">
-        <v>6412532</v>
+        <v>6412595</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,7 +3126,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3140,10 +3144,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129527675</v>
+        <v>129527753</v>
       </c>
       <c r="B25" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3183,10 +3187,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569104</v>
+        <v>569077</v>
       </c>
       <c r="R25" t="n">
-        <v>6412595</v>
+        <v>6412532</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3246,42 +3250,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129527732</v>
+        <v>129527675</v>
       </c>
       <c r="B26" t="n">
-        <v>57733</v>
+        <v>98778</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3289,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569083</v>
+        <v>569104</v>
       </c>
       <c r="R26" t="n">
-        <v>6412557</v>
+        <v>6412595</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3327,17 +3331,13 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Bearbetat gran</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>129527932</v>
       </c>
       <c r="B27" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>129527981</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>129528084</v>
       </c>
       <c r="B29" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>129528002</v>
       </c>
       <c r="B30" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>129527952</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>129528031</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129527700</v>
       </c>
       <c r="B3" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129527963</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129527842</v>
       </c>
       <c r="B5" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129527900</v>
       </c>
       <c r="B6" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129527787</v>
       </c>
       <c r="B7" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>129527859</v>
       </c>
       <c r="B8" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>129527942</v>
       </c>
       <c r="B9" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>129528060</v>
       </c>
       <c r="B10" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129527924</v>
+        <v>129528042</v>
       </c>
       <c r="B11" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569016</v>
+        <v>568999</v>
       </c>
       <c r="R11" t="n">
-        <v>6412795</v>
+        <v>6412827</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129528042</v>
+        <v>129527714</v>
       </c>
       <c r="B12" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568999</v>
+        <v>569077</v>
       </c>
       <c r="R12" t="n">
-        <v>6412827</v>
+        <v>6412589</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129527714</v>
+        <v>129527924</v>
       </c>
       <c r="B13" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569077</v>
+        <v>569016</v>
       </c>
       <c r="R13" t="n">
-        <v>6412589</v>
+        <v>6412795</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129527906</v>
+        <v>129527885</v>
       </c>
       <c r="B15" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569032</v>
+        <v>568987</v>
       </c>
       <c r="R15" t="n">
-        <v>6412788</v>
+        <v>6412775</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129527885</v>
+        <v>129527906</v>
       </c>
       <c r="B16" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>568987</v>
+        <v>569032</v>
       </c>
       <c r="R16" t="n">
-        <v>6412775</v>
+        <v>6412788</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2288,7 +2288,7 @@
         <v>129528013</v>
       </c>
       <c r="B17" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>129527636</v>
       </c>
       <c r="B18" t="n">
-        <v>92250</v>
+        <v>92252</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>129528074</v>
       </c>
       <c r="B19" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>129527910</v>
       </c>
       <c r="B20" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>129527766</v>
       </c>
       <c r="B21" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>129527872</v>
       </c>
       <c r="B22" t="n">
-        <v>92250</v>
+        <v>92252</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3043,38 +3043,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129528112</v>
+        <v>129527675</v>
       </c>
       <c r="B24" t="n">
-        <v>58106</v>
+        <v>98780</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3126,6 +3130,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3147,7 +3152,7 @@
         <v>129527753</v>
       </c>
       <c r="B25" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3250,42 +3255,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129527675</v>
+        <v>129528112</v>
       </c>
       <c r="B26" t="n">
-        <v>98778</v>
+        <v>58106</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3337,7 +3338,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>129527932</v>
       </c>
       <c r="B27" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,10 +3465,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129527981</v>
+        <v>129528084</v>
       </c>
       <c r="B28" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569004</v>
+        <v>569002</v>
       </c>
       <c r="R28" t="n">
-        <v>6412822</v>
+        <v>6412837</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,10 +3571,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129528084</v>
+        <v>129527981</v>
       </c>
       <c r="B29" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569002</v>
+        <v>569004</v>
       </c>
       <c r="R29" t="n">
-        <v>6412837</v>
+        <v>6412822</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3680,7 +3680,7 @@
         <v>129528002</v>
       </c>
       <c r="B30" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3783,10 +3783,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129527952</v>
+        <v>129528031</v>
       </c>
       <c r="B31" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569027</v>
+        <v>568997</v>
       </c>
       <c r="R31" t="n">
-        <v>6412813</v>
+        <v>6412845</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,10 +3889,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129528031</v>
+        <v>129527952</v>
       </c>
       <c r="B32" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>568997</v>
+        <v>569027</v>
       </c>
       <c r="R32" t="n">
-        <v>6412845</v>
+        <v>6412813</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129527700</v>
       </c>
       <c r="B3" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129527963</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129527842</v>
       </c>
       <c r="B5" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129527900</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129527787</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>129527942</v>
       </c>
       <c r="B9" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>129528060</v>
       </c>
       <c r="B10" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129528042</v>
+        <v>129527924</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568999</v>
+        <v>569016</v>
       </c>
       <c r="R11" t="n">
-        <v>6412827</v>
+        <v>6412795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129527714</v>
+        <v>129528042</v>
       </c>
       <c r="B12" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569077</v>
+        <v>568999</v>
       </c>
       <c r="R12" t="n">
-        <v>6412589</v>
+        <v>6412827</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129527924</v>
+        <v>129527714</v>
       </c>
       <c r="B13" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569016</v>
+        <v>569077</v>
       </c>
       <c r="R13" t="n">
-        <v>6412795</v>
+        <v>6412589</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129527885</v>
+        <v>129527906</v>
       </c>
       <c r="B15" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568987</v>
+        <v>569032</v>
       </c>
       <c r="R15" t="n">
-        <v>6412775</v>
+        <v>6412788</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129527906</v>
+        <v>129527885</v>
       </c>
       <c r="B16" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569032</v>
+        <v>568987</v>
       </c>
       <c r="R16" t="n">
-        <v>6412788</v>
+        <v>6412775</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2506,7 +2506,7 @@
         <v>129528074</v>
       </c>
       <c r="B19" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>129527910</v>
       </c>
       <c r="B20" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2933,27 +2933,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129527732</v>
+        <v>129528112</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>58106</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2964,11 +2964,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2976,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569083</v>
+        <v>569104</v>
       </c>
       <c r="R23" t="n">
-        <v>6412557</v>
+        <v>6412595</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,11 +3008,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Bearbetat gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,42 +3034,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129527675</v>
+        <v>129527732</v>
       </c>
       <c r="B24" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3086,10 +3077,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569104</v>
+        <v>569083</v>
       </c>
       <c r="R24" t="n">
-        <v>6412595</v>
+        <v>6412557</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,13 +3115,17 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3152,7 +3147,7 @@
         <v>129527753</v>
       </c>
       <c r="B25" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3255,38 +3250,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129528112</v>
+        <v>129527675</v>
       </c>
       <c r="B26" t="n">
-        <v>58106</v>
+        <v>98790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3338,6 +3337,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3465,10 +3465,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129528084</v>
+        <v>129527981</v>
       </c>
       <c r="B28" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569002</v>
+        <v>569004</v>
       </c>
       <c r="R28" t="n">
-        <v>6412837</v>
+        <v>6412822</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,10 +3571,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129527981</v>
+        <v>129528084</v>
       </c>
       <c r="B29" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569004</v>
+        <v>569002</v>
       </c>
       <c r="R29" t="n">
-        <v>6412822</v>
+        <v>6412837</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3680,7 +3680,7 @@
         <v>129528002</v>
       </c>
       <c r="B30" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3783,10 +3783,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129528031</v>
+        <v>129527952</v>
       </c>
       <c r="B31" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>568997</v>
+        <v>569027</v>
       </c>
       <c r="R31" t="n">
-        <v>6412845</v>
+        <v>6412813</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,10 +3889,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129527952</v>
+        <v>129528031</v>
       </c>
       <c r="B32" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569027</v>
+        <v>568997</v>
       </c>
       <c r="R32" t="n">
-        <v>6412813</v>
+        <v>6412845</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -2933,27 +2933,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129528112</v>
+        <v>129527732</v>
       </c>
       <c r="B23" t="n">
-        <v>58106</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2964,7 +2964,11 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2972,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569104</v>
+        <v>569083</v>
       </c>
       <c r="R23" t="n">
-        <v>6412595</v>
+        <v>6412557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3008,6 +3012,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3034,42 +3043,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129527732</v>
+        <v>129527753</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>98790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3077,10 +3086,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569083</v>
+        <v>569077</v>
       </c>
       <c r="R24" t="n">
-        <v>6412557</v>
+        <v>6412532</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3115,17 +3124,13 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bearbetat gran</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3144,7 +3149,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129527753</v>
+        <v>129527675</v>
       </c>
       <c r="B25" t="n">
         <v>98790</v>
@@ -3187,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569077</v>
+        <v>569104</v>
       </c>
       <c r="R25" t="n">
-        <v>6412532</v>
+        <v>6412595</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3250,42 +3255,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129527675</v>
+        <v>129528112</v>
       </c>
       <c r="B26" t="n">
-        <v>98790</v>
+        <v>58106</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3337,7 +3338,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -4211,7 +4211,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134260796</v>
+        <v>134260718</v>
       </c>
       <c r="B35" t="n">
         <v>99181</v>
@@ -4254,10 +4254,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569026</v>
+        <v>569024</v>
       </c>
       <c r="R35" t="n">
-        <v>6412830</v>
+        <v>6412797</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134260718</v>
+        <v>134260796</v>
       </c>
       <c r="B36" t="n">
         <v>99181</v>
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569024</v>
+        <v>569026</v>
       </c>
       <c r="R36" t="n">
-        <v>6412797</v>
+        <v>6412830</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5184,7 +5184,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134260782</v>
+        <v>134260766</v>
       </c>
       <c r="B44" t="n">
         <v>99181</v>
@@ -5223,14 +5223,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>A 48739, Karrum, Sm</t>
+          <t>Knärot, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569027</v>
+        <v>569015</v>
       </c>
       <c r="R44" t="n">
-        <v>6412827</v>
+        <v>6412814</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5290,7 +5290,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134260766</v>
+        <v>134260782</v>
       </c>
       <c r="B45" t="n">
         <v>99181</v>
@@ -5329,14 +5329,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Knärot, Sm</t>
+          <t>A 48739, Karrum, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569015</v>
+        <v>569027</v>
       </c>
       <c r="R45" t="n">
-        <v>6412814</v>
+        <v>6412827</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -4108,7 +4108,7 @@
         <v>134260905</v>
       </c>
       <c r="B34" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4211,42 +4211,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134260718</v>
+        <v>134260521</v>
       </c>
       <c r="B35" t="n">
-        <v>99181</v>
+        <v>57972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4254,10 +4254,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569024</v>
+        <v>569084</v>
       </c>
       <c r="R35" t="n">
-        <v>6412797</v>
+        <v>6412558</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4292,13 +4292,17 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4320,7 +4324,7 @@
         <v>134260796</v>
       </c>
       <c r="B36" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4423,10 +4427,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134260861</v>
+        <v>134260718</v>
       </c>
       <c r="B37" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4466,10 +4470,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569019</v>
+        <v>569024</v>
       </c>
       <c r="R37" t="n">
-        <v>6412826</v>
+        <v>6412797</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4529,42 +4533,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134260521</v>
+        <v>134260861</v>
       </c>
       <c r="B38" t="n">
-        <v>57972</v>
+        <v>99188</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4572,10 +4576,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569084</v>
+        <v>569019</v>
       </c>
       <c r="R38" t="n">
-        <v>6412558</v>
+        <v>6412826</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4610,17 +4614,13 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>134260737</v>
       </c>
       <c r="B39" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>134260823</v>
       </c>
       <c r="B41" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>134260443</v>
       </c>
       <c r="B43" t="n">
-        <v>99156</v>
+        <v>99163</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5184,10 +5184,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134260766</v>
+        <v>134260782</v>
       </c>
       <c r="B44" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5223,14 +5223,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Knärot, Sm</t>
+          <t>A 48739, Karrum, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569015</v>
+        <v>569027</v>
       </c>
       <c r="R44" t="n">
-        <v>6412814</v>
+        <v>6412827</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5290,10 +5290,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134260782</v>
+        <v>134260766</v>
       </c>
       <c r="B45" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5329,14 +5329,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>A 48739, Karrum, Sm</t>
+          <t>Knärot, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569027</v>
+        <v>569015</v>
       </c>
       <c r="R45" t="n">
-        <v>6412827</v>
+        <v>6412814</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5399,7 +5399,7 @@
         <v>134260839</v>
       </c>
       <c r="B46" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>134260725</v>
       </c>
       <c r="B47" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>134260879</v>
       </c>
       <c r="B48" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>134260809</v>
       </c>
       <c r="B50" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>134260654</v>
       </c>
       <c r="B51" t="n">
-        <v>106310</v>
+        <v>106317</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74604083</v>
+        <v>134260679</v>
       </c>
       <c r="B2" t="n">
-        <v>97543</v>
+        <v>92188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>3008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra bro 700 m V, Sm</t>
+          <t>A 48739, Karrum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569033</v>
+        <v>568990</v>
       </c>
       <c r="R2" t="n">
-        <v>6412653</v>
+        <v>6412826</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1987-12-31</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G2e 4012. SOM: Lycopodium clavatum. LEG: Gunvald Bruce</t>
+          <t>På grov tallåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,69 +770,64 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskogsstig</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129527700</v>
+        <v>129527766</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569070</v>
+        <v>569036</v>
       </c>
       <c r="R3" t="n">
-        <v>6412584</v>
+        <v>6412522</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,42 +898,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129527963</v>
+        <v>129527859</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569023</v>
+        <v>569043</v>
       </c>
       <c r="R4" t="n">
-        <v>6412835</v>
+        <v>6412642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,46 +1007,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129527842</v>
+        <v>129527613</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569057</v>
+        <v>569199</v>
       </c>
       <c r="R5" t="n">
-        <v>6412642</v>
+        <v>6412402</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,42 +1116,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129527900</v>
+        <v>129527932</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569029</v>
+        <v>569016</v>
       </c>
       <c r="R6" t="n">
-        <v>6412790</v>
+        <v>6412795</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,46 +1225,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129527787</v>
+        <v>129528013</v>
       </c>
       <c r="B7" t="n">
-        <v>98790</v>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1261,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569153</v>
+        <v>569019</v>
       </c>
       <c r="R7" t="n">
-        <v>6412439</v>
+        <v>6412824</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129527859</v>
+        <v>129527636</v>
       </c>
       <c r="B8" t="n">
-        <v>92881</v>
+        <v>92567</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,26 +1345,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1370,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569043</v>
+        <v>569145</v>
       </c>
       <c r="R8" t="n">
-        <v>6412642</v>
+        <v>6412521</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,42 +1443,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129527942</v>
+        <v>129527872</v>
       </c>
       <c r="B9" t="n">
-        <v>98790</v>
+        <v>92567</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1476,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569019</v>
+        <v>569039</v>
       </c>
       <c r="R9" t="n">
-        <v>6412827</v>
+        <v>6412677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,42 +1552,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129528060</v>
+        <v>129527594</v>
       </c>
       <c r="B10" t="n">
-        <v>98790</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1582,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569004</v>
+        <v>569183</v>
       </c>
       <c r="R10" t="n">
-        <v>6412825</v>
+        <v>6412425</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,13 +1633,17 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökt i stubbe</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1645,42 +1662,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129527924</v>
+        <v>129527732</v>
       </c>
       <c r="B11" t="n">
-        <v>98790</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1688,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569016</v>
+        <v>569083</v>
       </c>
       <c r="R11" t="n">
-        <v>6412795</v>
+        <v>6412557</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1726,13 +1743,17 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bearbetat gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1751,42 +1772,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129528042</v>
+        <v>129527808</v>
       </c>
       <c r="B12" t="n">
-        <v>98790</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1794,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568999</v>
+        <v>569157</v>
       </c>
       <c r="R12" t="n">
-        <v>6412827</v>
+        <v>6412484</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,13 +1853,17 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1857,42 +1882,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129527714</v>
+        <v>134260500</v>
       </c>
       <c r="B13" t="n">
-        <v>98790</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1900,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569077</v>
+        <v>569157</v>
       </c>
       <c r="R13" t="n">
-        <v>6412589</v>
+        <v>6412502</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,12 +1955,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,7 +1974,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1963,14 +1992,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129527808</v>
+        <v>134260521</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1996,7 +2025,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2006,10 +2035,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569157</v>
+        <v>569084</v>
       </c>
       <c r="R14" t="n">
-        <v>6412484</v>
+        <v>6412558</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,17 +2065,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Bearbetat stubbe</t>
+          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,42 +2102,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129527906</v>
+        <v>129527917</v>
       </c>
       <c r="B15" t="n">
-        <v>98790</v>
+        <v>58067</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100090</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2116,13 +2149,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569032</v>
+        <v>569026</v>
       </c>
       <c r="R15" t="n">
-        <v>6412788</v>
+        <v>6412804</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2160,7 +2193,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2179,42 +2211,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129527885</v>
+        <v>129528112</v>
       </c>
       <c r="B16" t="n">
-        <v>98790</v>
+        <v>58327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2222,10 +2250,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>568987</v>
+        <v>569104</v>
       </c>
       <c r="R16" t="n">
-        <v>6412775</v>
+        <v>6412595</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,7 +2294,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2285,10 +2312,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129528013</v>
+        <v>134260608</v>
       </c>
       <c r="B17" t="n">
-        <v>92919</v>
+        <v>58136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,48 +2323,53 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 48739, Karrum, Sm</t>
+          <t>A48739, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569019</v>
+        <v>569157</v>
       </c>
       <c r="R17" t="n">
-        <v>6412824</v>
+        <v>6412498</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2361,12 +2393,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ad med minst 4 utflugna ungar i liten flock.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,7 +2412,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2394,10 +2430,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129527636</v>
+        <v>134261001</v>
       </c>
       <c r="B18" t="n">
-        <v>92252</v>
+        <v>58131</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2405,34 +2441,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6031</v>
+        <v>103023</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2440,10 +2469,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569145</v>
+        <v>569104</v>
       </c>
       <c r="R18" t="n">
-        <v>6412521</v>
+        <v>6412595</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2470,12 +2499,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,7 +2513,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2503,42 +2531,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129528074</v>
+        <v>134260971</v>
       </c>
       <c r="B19" t="n">
-        <v>98790</v>
+        <v>58658</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2546,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568997</v>
+        <v>569104</v>
       </c>
       <c r="R19" t="n">
-        <v>6412826</v>
+        <v>6412595</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2576,12 +2600,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2590,7 +2614,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2609,41 +2632,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129527910</v>
+        <v>134260443</v>
       </c>
       <c r="B20" t="n">
-        <v>98790</v>
+        <v>99170</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>219797</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2652,10 +2683,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569026</v>
+        <v>569179</v>
       </c>
       <c r="R20" t="n">
-        <v>6412804</v>
+        <v>6412470</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2682,12 +2713,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2715,45 +2746,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129527766</v>
+        <v>129527675</v>
       </c>
       <c r="B21" t="n">
-        <v>92881</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2761,10 +2789,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569036</v>
+        <v>569104</v>
       </c>
       <c r="R21" t="n">
-        <v>6412522</v>
+        <v>6412595</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2824,45 +2852,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129527872</v>
+        <v>129527700</v>
       </c>
       <c r="B22" t="n">
-        <v>92252</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2870,10 +2895,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569039</v>
+        <v>569070</v>
       </c>
       <c r="R22" t="n">
-        <v>6412677</v>
+        <v>6412584</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2933,42 +2958,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129527732</v>
+        <v>129527714</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2976,10 +3001,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569083</v>
+        <v>569077</v>
       </c>
       <c r="R23" t="n">
-        <v>6412557</v>
+        <v>6412589</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,17 +3039,13 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Bearbetat gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3046,7 +3067,7 @@
         <v>129527753</v>
       </c>
       <c r="B24" t="n">
-        <v>98790</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3149,10 +3170,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129527675</v>
+        <v>129527787</v>
       </c>
       <c r="B25" t="n">
-        <v>98790</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3177,7 +3198,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -3192,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569104</v>
+        <v>569153</v>
       </c>
       <c r="R25" t="n">
-        <v>6412595</v>
+        <v>6412439</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,38 +3280,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129528112</v>
+        <v>129527842</v>
       </c>
       <c r="B26" t="n">
-        <v>58106</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3294,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569104</v>
+        <v>569057</v>
       </c>
       <c r="R26" t="n">
-        <v>6412595</v>
+        <v>6412642</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3338,6 +3371,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3356,45 +3390,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129527932</v>
+        <v>129527885</v>
       </c>
       <c r="B27" t="n">
-        <v>92919</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3402,10 +3433,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569016</v>
+        <v>568987</v>
       </c>
       <c r="R27" t="n">
-        <v>6412795</v>
+        <v>6412775</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3465,10 +3496,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129527981</v>
+        <v>129527900</v>
       </c>
       <c r="B28" t="n">
-        <v>98790</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3508,10 +3539,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569004</v>
+        <v>569029</v>
       </c>
       <c r="R28" t="n">
-        <v>6412822</v>
+        <v>6412790</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,10 +3602,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129528084</v>
+        <v>129527906</v>
       </c>
       <c r="B29" t="n">
-        <v>98790</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3614,10 +3645,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569002</v>
+        <v>569032</v>
       </c>
       <c r="R29" t="n">
-        <v>6412837</v>
+        <v>6412788</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3677,10 +3708,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129528002</v>
+        <v>129527910</v>
       </c>
       <c r="B30" t="n">
-        <v>98790</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,10 +3751,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569016</v>
+        <v>569026</v>
       </c>
       <c r="R30" t="n">
-        <v>6412840</v>
+        <v>6412804</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,10 +3814,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129527952</v>
+        <v>129527924</v>
       </c>
       <c r="B31" t="n">
-        <v>98790</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3826,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569027</v>
+        <v>569016</v>
       </c>
       <c r="R31" t="n">
-        <v>6412813</v>
+        <v>6412795</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,10 +3920,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129528031</v>
+        <v>129527942</v>
       </c>
       <c r="B32" t="n">
-        <v>98790</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3932,10 +3963,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>568997</v>
+        <v>569019</v>
       </c>
       <c r="R32" t="n">
-        <v>6412845</v>
+        <v>6412827</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3995,42 +4026,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129527594</v>
+        <v>129527952</v>
       </c>
       <c r="B33" t="n">
-        <v>57733</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4038,10 +4069,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569183</v>
+        <v>569027</v>
       </c>
       <c r="R33" t="n">
-        <v>6412425</v>
+        <v>6412813</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4076,17 +4107,13 @@
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Födosökt i stubbe</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4105,10 +4132,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134260905</v>
+        <v>129527963</v>
       </c>
       <c r="B34" t="n">
-        <v>99188</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4148,10 +4175,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569004</v>
+        <v>569023</v>
       </c>
       <c r="R34" t="n">
-        <v>6412850</v>
+        <v>6412835</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4178,12 +4205,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4211,42 +4238,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134260521</v>
+        <v>129527981</v>
       </c>
       <c r="B35" t="n">
-        <v>57972</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4254,10 +4281,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569084</v>
+        <v>569004</v>
       </c>
       <c r="R35" t="n">
-        <v>6412558</v>
+        <v>6412822</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4284,17 +4311,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,6 +4325,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4321,10 +4344,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134260796</v>
+        <v>129528002</v>
       </c>
       <c r="B36" t="n">
-        <v>99188</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4364,10 +4387,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569026</v>
+        <v>569016</v>
       </c>
       <c r="R36" t="n">
-        <v>6412830</v>
+        <v>6412840</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4394,12 +4417,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4427,10 +4450,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134260718</v>
+        <v>129528031</v>
       </c>
       <c r="B37" t="n">
-        <v>99188</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4470,10 +4493,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569024</v>
+        <v>568997</v>
       </c>
       <c r="R37" t="n">
-        <v>6412797</v>
+        <v>6412845</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4500,12 +4523,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4533,10 +4556,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134260861</v>
+        <v>129528042</v>
       </c>
       <c r="B38" t="n">
-        <v>99188</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4576,10 +4599,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569019</v>
+        <v>568999</v>
       </c>
       <c r="R38" t="n">
-        <v>6412826</v>
+        <v>6412827</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4606,12 +4629,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,10 +4662,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134260737</v>
+        <v>129528060</v>
       </c>
       <c r="B39" t="n">
-        <v>99188</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4682,10 +4705,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569025</v>
+        <v>569004</v>
       </c>
       <c r="R39" t="n">
-        <v>6412806</v>
+        <v>6412825</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4712,12 +4735,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4745,38 +4768,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134260971</v>
+        <v>129528074</v>
       </c>
       <c r="B40" t="n">
-        <v>58658</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4784,10 +4811,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569104</v>
+        <v>568997</v>
       </c>
       <c r="R40" t="n">
-        <v>6412595</v>
+        <v>6412826</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4814,12 +4841,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4828,6 +4855,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4846,10 +4874,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134260823</v>
+        <v>129528084</v>
       </c>
       <c r="B41" t="n">
-        <v>99188</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4889,10 +4917,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569017</v>
+        <v>569002</v>
       </c>
       <c r="R41" t="n">
-        <v>6412824</v>
+        <v>6412837</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4919,12 +4947,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4952,64 +4980,56 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134260628</v>
+        <v>134260718</v>
       </c>
       <c r="B42" t="n">
-        <v>58136</v>
+        <v>99195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>A48739, Sm</t>
+          <t>A 48739, Karrum, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569157</v>
+        <v>569024</v>
       </c>
       <c r="R42" t="n">
-        <v>6412498</v>
+        <v>6412797</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5041,17 +5061,13 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Liten familjeflock. Trol föräldrar med utflugna ungar.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5070,49 +5086,41 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134260443</v>
+        <v>134260725</v>
       </c>
       <c r="B43" t="n">
-        <v>99163</v>
+        <v>99195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219797</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5121,10 +5129,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569179</v>
+        <v>569018</v>
       </c>
       <c r="R43" t="n">
-        <v>6412470</v>
+        <v>6412785</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5184,10 +5192,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134260782</v>
+        <v>134260737</v>
       </c>
       <c r="B44" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5227,10 +5235,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569027</v>
+        <v>569025</v>
       </c>
       <c r="R44" t="n">
-        <v>6412827</v>
+        <v>6412806</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5293,7 +5301,7 @@
         <v>134260766</v>
       </c>
       <c r="B45" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5396,10 +5404,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134260839</v>
+        <v>134260782</v>
       </c>
       <c r="B46" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5439,10 +5447,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569014</v>
+        <v>569027</v>
       </c>
       <c r="R46" t="n">
-        <v>6412830</v>
+        <v>6412827</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5502,10 +5510,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134260725</v>
+        <v>134260796</v>
       </c>
       <c r="B47" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5545,10 +5553,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569018</v>
+        <v>569026</v>
       </c>
       <c r="R47" t="n">
-        <v>6412785</v>
+        <v>6412830</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5608,10 +5616,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134260879</v>
+        <v>134260809</v>
       </c>
       <c r="B48" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5651,10 +5659,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>568999</v>
+        <v>569014</v>
       </c>
       <c r="R48" t="n">
-        <v>6412852</v>
+        <v>6412831</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5714,42 +5722,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134260500</v>
+        <v>134260823</v>
       </c>
       <c r="B49" t="n">
-        <v>57972</v>
+        <v>99195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5757,10 +5765,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569157</v>
+        <v>569017</v>
       </c>
       <c r="R49" t="n">
-        <v>6412502</v>
+        <v>6412824</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5795,17 +5803,13 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5824,10 +5828,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134260809</v>
+        <v>134260839</v>
       </c>
       <c r="B50" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5870,7 +5874,7 @@
         <v>569014</v>
       </c>
       <c r="R50" t="n">
-        <v>6412831</v>
+        <v>6412830</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5930,49 +5934,41 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134260654</v>
+        <v>134260861</v>
       </c>
       <c r="B51" t="n">
-        <v>106317</v>
+        <v>99195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
@@ -5981,10 +5977,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569022</v>
+        <v>569019</v>
       </c>
       <c r="R51" t="n">
-        <v>6412800</v>
+        <v>6412826</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6019,11 +6015,6 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ca 10 knoppar/blommor</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6046,6 +6037,448 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>134260879</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>568999</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6412852</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>134260905</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>569004</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6412850</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134260654</v>
+      </c>
+      <c r="B54" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>A 48739, Karrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>569022</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6412800</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ca 10 knoppar/blommor</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>74604083</v>
+      </c>
+      <c r="B55" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Västra bro 700 m V, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>569033</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6412653</v>
+      </c>
+      <c r="S55" t="n">
+        <v>50</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>1983-01-01</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>1987-12-31</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7G2e 4012. SOM: Lycopodium clavatum. LEG: Gunvald Bruce</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Barrskogsstig</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ54"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2172,27 +2172,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129528112</v>
+        <v>129527917</v>
       </c>
       <c r="B15" t="n">
-        <v>58327</v>
+        <v>58094</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>100090</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2200,10 +2200,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2211,13 +2219,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569104</v>
+        <v>569026</v>
       </c>
       <c r="R15" t="n">
-        <v>6412595</v>
+        <v>6412804</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2272,70 +2280,58 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129528112</t>
+          <t>https://artportalen.se/Sighting/129527917</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134260608</v>
+        <v>129528112</v>
       </c>
       <c r="B16" t="n">
-        <v>58136</v>
+        <v>58327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>föda åt ungar</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A48739, Sm</t>
+          <t>A 48739, Karrum, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569157</v>
+        <v>569104</v>
       </c>
       <c r="R16" t="n">
-        <v>6412498</v>
+        <v>6412595</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2359,17 +2355,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ad med minst 4 utflugna ungar i liten flock.</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,58 +2386,70 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134260608</t>
+          <t>https://artportalen.se/Sighting/129528112</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134261001</v>
+        <v>134260608</v>
       </c>
       <c r="B17" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 48739, Karrum, Sm</t>
+          <t>A48739, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569104</v>
+        <v>569157</v>
       </c>
       <c r="R17" t="n">
-        <v>6412595</v>
+        <v>6412498</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2476,6 +2479,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ad med minst 4 utflugna ungar i liten flock.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2501,16 +2509,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134261001</t>
+          <t>https://artportalen.se/Sighting/134260608</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134260971</v>
+        <v>134261001</v>
       </c>
       <c r="B18" t="n">
-        <v>58658</v>
+        <v>58131</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2518,16 +2526,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103044</v>
+        <v>103023</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2607,16 +2615,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134260971</t>
+          <t>https://artportalen.se/Sighting/134261001</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134260443</v>
+        <v>134260971</v>
       </c>
       <c r="B19" t="n">
-        <v>99170</v>
+        <v>58658</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,39 +2632,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219797</v>
+        <v>103044</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2664,10 +2660,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569179</v>
+        <v>569104</v>
       </c>
       <c r="R19" t="n">
-        <v>6412470</v>
+        <v>6412595</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2708,7 +2704,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2726,47 +2721,55 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134260443</t>
+          <t>https://artportalen.se/Sighting/134260971</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129527675</v>
+        <v>134260443</v>
       </c>
       <c r="B20" t="n">
-        <v>99118</v>
+        <v>99170</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>219797</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2775,10 +2778,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569104</v>
+        <v>569179</v>
       </c>
       <c r="R20" t="n">
-        <v>6412595</v>
+        <v>6412470</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2805,12 +2808,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,13 +2840,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129527675</t>
+          <t>https://artportalen.se/Sighting/134260443</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129527700</v>
+        <v>129527675</v>
       </c>
       <c r="B21" t="n">
         <v>99118</v>
@@ -2886,10 +2889,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569070</v>
+        <v>569104</v>
       </c>
       <c r="R21" t="n">
-        <v>6412584</v>
+        <v>6412595</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,13 +2951,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129527700</t>
+          <t>https://artportalen.se/Sighting/129527675</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129527714</v>
+        <v>129527700</v>
       </c>
       <c r="B22" t="n">
         <v>99118</v>
@@ -2997,10 +3000,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569077</v>
+        <v>569070</v>
       </c>
       <c r="R22" t="n">
-        <v>6412589</v>
+        <v>6412584</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,13 +3062,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129527714</t>
+          <t>https://artportalen.se/Sighting/129527700</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129527753</v>
+        <v>129527714</v>
       </c>
       <c r="B23" t="n">
         <v>99118</v>
@@ -3111,7 +3114,7 @@
         <v>569077</v>
       </c>
       <c r="R23" t="n">
-        <v>6412532</v>
+        <v>6412589</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3170,13 +3173,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129527753</t>
+          <t>https://artportalen.se/Sighting/129527714</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129527787</v>
+        <v>129527753</v>
       </c>
       <c r="B24" t="n">
         <v>99118</v>
@@ -3204,11 +3207,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -3223,10 +3222,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569153</v>
+        <v>569077</v>
       </c>
       <c r="R24" t="n">
-        <v>6412439</v>
+        <v>6412532</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3285,13 +3284,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129527787</t>
+          <t>https://artportalen.se/Sighting/129527753</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129527842</v>
+        <v>129527787</v>
       </c>
       <c r="B25" t="n">
         <v>99118</v>
@@ -3321,7 +3320,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3338,10 +3337,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569057</v>
+        <v>569153</v>
       </c>
       <c r="R25" t="n">
-        <v>6412642</v>
+        <v>6412439</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3400,13 +3399,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129527842</t>
+          <t>https://artportalen.se/Sighting/129527787</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129527885</v>
+        <v>129527842</v>
       </c>
       <c r="B26" t="n">
         <v>99118</v>
@@ -3434,7 +3433,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -3449,10 +3452,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568987</v>
+        <v>569057</v>
       </c>
       <c r="R26" t="n">
-        <v>6412775</v>
+        <v>6412642</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3511,13 +3514,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129527885</t>
+          <t>https://artportalen.se/Sighting/129527842</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129527900</v>
+        <v>129527885</v>
       </c>
       <c r="B27" t="n">
         <v>99118</v>
@@ -3560,10 +3563,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569029</v>
+        <v>568987</v>
       </c>
       <c r="R27" t="n">
-        <v>6412790</v>
+        <v>6412775</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3622,13 +3625,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129527900</t>
+          <t>https://artportalen.se/Sighting/129527885</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129527906</v>
+        <v>129527900</v>
       </c>
       <c r="B28" t="n">
         <v>99118</v>
@@ -3671,10 +3674,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569032</v>
+        <v>569029</v>
       </c>
       <c r="R28" t="n">
-        <v>6412788</v>
+        <v>6412790</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3733,13 +3736,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129527906</t>
+          <t>https://artportalen.se/Sighting/129527900</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129527910</v>
+        <v>129527906</v>
       </c>
       <c r="B29" t="n">
         <v>99118</v>
@@ -3782,10 +3785,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569026</v>
+        <v>569032</v>
       </c>
       <c r="R29" t="n">
-        <v>6412804</v>
+        <v>6412788</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3844,13 +3847,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129527910</t>
+          <t>https://artportalen.se/Sighting/129527906</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129527924</v>
+        <v>129527910</v>
       </c>
       <c r="B30" t="n">
         <v>99118</v>
@@ -3893,10 +3896,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569016</v>
+        <v>569026</v>
       </c>
       <c r="R30" t="n">
-        <v>6412795</v>
+        <v>6412804</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3955,13 +3958,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129527924</t>
+          <t>https://artportalen.se/Sighting/129527910</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129527942</v>
+        <v>129527924</v>
       </c>
       <c r="B31" t="n">
         <v>99118</v>
@@ -4004,10 +4007,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569019</v>
+        <v>569016</v>
       </c>
       <c r="R31" t="n">
-        <v>6412827</v>
+        <v>6412795</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4066,13 +4069,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129527942</t>
+          <t>https://artportalen.se/Sighting/129527924</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129527952</v>
+        <v>129527942</v>
       </c>
       <c r="B32" t="n">
         <v>99118</v>
@@ -4115,10 +4118,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569027</v>
+        <v>569019</v>
       </c>
       <c r="R32" t="n">
-        <v>6412813</v>
+        <v>6412827</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4177,13 +4180,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129527952</t>
+          <t>https://artportalen.se/Sighting/129527942</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129527963</v>
+        <v>129527952</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -4226,10 +4229,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569023</v>
+        <v>569027</v>
       </c>
       <c r="R33" t="n">
-        <v>6412835</v>
+        <v>6412813</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4288,13 +4291,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129527963</t>
+          <t>https://artportalen.se/Sighting/129527952</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129527981</v>
+        <v>129527963</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -4337,10 +4340,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569004</v>
+        <v>569023</v>
       </c>
       <c r="R34" t="n">
-        <v>6412822</v>
+        <v>6412835</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4399,13 +4402,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129527981</t>
+          <t>https://artportalen.se/Sighting/129527963</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129528002</v>
+        <v>129527981</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4448,10 +4451,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569016</v>
+        <v>569004</v>
       </c>
       <c r="R35" t="n">
-        <v>6412840</v>
+        <v>6412822</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4510,13 +4513,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129528002</t>
+          <t>https://artportalen.se/Sighting/129527981</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129528031</v>
+        <v>129528002</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4559,10 +4562,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>568997</v>
+        <v>569016</v>
       </c>
       <c r="R36" t="n">
-        <v>6412845</v>
+        <v>6412840</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4621,13 +4624,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129528031</t>
+          <t>https://artportalen.se/Sighting/129528002</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129528042</v>
+        <v>129528031</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4670,10 +4673,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>568999</v>
+        <v>568997</v>
       </c>
       <c r="R37" t="n">
-        <v>6412827</v>
+        <v>6412845</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4732,13 +4735,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129528042</t>
+          <t>https://artportalen.se/Sighting/129528031</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129528060</v>
+        <v>129528042</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -4781,10 +4784,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569004</v>
+        <v>568999</v>
       </c>
       <c r="R38" t="n">
-        <v>6412825</v>
+        <v>6412827</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4843,13 +4846,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129528060</t>
+          <t>https://artportalen.se/Sighting/129528042</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129528074</v>
+        <v>129528060</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -4892,10 +4895,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>568997</v>
+        <v>569004</v>
       </c>
       <c r="R39" t="n">
-        <v>6412826</v>
+        <v>6412825</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4954,13 +4957,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129528074</t>
+          <t>https://artportalen.se/Sighting/129528060</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129528084</v>
+        <v>129528074</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -5003,10 +5006,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569002</v>
+        <v>568997</v>
       </c>
       <c r="R40" t="n">
-        <v>6412837</v>
+        <v>6412826</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5065,16 +5068,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129528084</t>
+          <t>https://artportalen.se/Sighting/129528074</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134260718</v>
+        <v>129528084</v>
       </c>
       <c r="B41" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,10 +5117,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569024</v>
+        <v>569002</v>
       </c>
       <c r="R41" t="n">
-        <v>6412797</v>
+        <v>6412837</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5144,12 +5147,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5176,13 +5179,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134260718</t>
+          <t>https://artportalen.se/Sighting/129528084</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134260725</v>
+        <v>134260718</v>
       </c>
       <c r="B42" t="n">
         <v>99195</v>
@@ -5225,10 +5228,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569018</v>
+        <v>569024</v>
       </c>
       <c r="R42" t="n">
-        <v>6412785</v>
+        <v>6412797</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5287,13 +5290,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134260725</t>
+          <t>https://artportalen.se/Sighting/134260718</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134260737</v>
+        <v>134260725</v>
       </c>
       <c r="B43" t="n">
         <v>99195</v>
@@ -5336,10 +5339,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569025</v>
+        <v>569018</v>
       </c>
       <c r="R43" t="n">
-        <v>6412806</v>
+        <v>6412785</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5398,13 +5401,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134260737</t>
+          <t>https://artportalen.se/Sighting/134260725</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134260766</v>
+        <v>134260737</v>
       </c>
       <c r="B44" t="n">
         <v>99195</v>
@@ -5443,14 +5446,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Knärot, Sm</t>
+          <t>A 48739, Karrum, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569015</v>
+        <v>569025</v>
       </c>
       <c r="R44" t="n">
-        <v>6412814</v>
+        <v>6412806</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5509,13 +5512,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134260766</t>
+          <t>https://artportalen.se/Sighting/134260737</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134260782</v>
+        <v>134260766</v>
       </c>
       <c r="B45" t="n">
         <v>99195</v>
@@ -5554,14 +5557,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>A 48739, Karrum, Sm</t>
+          <t>Knärot, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569027</v>
+        <v>569015</v>
       </c>
       <c r="R45" t="n">
-        <v>6412827</v>
+        <v>6412814</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5620,13 +5623,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134260782</t>
+          <t>https://artportalen.se/Sighting/134260766</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134260796</v>
+        <v>134260782</v>
       </c>
       <c r="B46" t="n">
         <v>99195</v>
@@ -5669,10 +5672,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569026</v>
+        <v>569027</v>
       </c>
       <c r="R46" t="n">
-        <v>6412830</v>
+        <v>6412827</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5731,13 +5734,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134260796</t>
+          <t>https://artportalen.se/Sighting/134260782</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134260809</v>
+        <v>134260796</v>
       </c>
       <c r="B47" t="n">
         <v>99195</v>
@@ -5780,10 +5783,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569014</v>
+        <v>569026</v>
       </c>
       <c r="R47" t="n">
-        <v>6412831</v>
+        <v>6412830</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5842,13 +5845,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134260809</t>
+          <t>https://artportalen.se/Sighting/134260796</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134260823</v>
+        <v>134260809</v>
       </c>
       <c r="B48" t="n">
         <v>99195</v>
@@ -5891,10 +5894,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569017</v>
+        <v>569014</v>
       </c>
       <c r="R48" t="n">
-        <v>6412824</v>
+        <v>6412831</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5953,13 +5956,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134260823</t>
+          <t>https://artportalen.se/Sighting/134260809</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134260839</v>
+        <v>134260823</v>
       </c>
       <c r="B49" t="n">
         <v>99195</v>
@@ -6002,10 +6005,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569014</v>
+        <v>569017</v>
       </c>
       <c r="R49" t="n">
-        <v>6412830</v>
+        <v>6412824</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6064,13 +6067,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134260839</t>
+          <t>https://artportalen.se/Sighting/134260823</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134260861</v>
+        <v>134260839</v>
       </c>
       <c r="B50" t="n">
         <v>99195</v>
@@ -6113,10 +6116,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569019</v>
+        <v>569014</v>
       </c>
       <c r="R50" t="n">
-        <v>6412826</v>
+        <v>6412830</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6175,13 +6178,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134260861</t>
+          <t>https://artportalen.se/Sighting/134260839</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134260879</v>
+        <v>134260861</v>
       </c>
       <c r="B51" t="n">
         <v>99195</v>
@@ -6224,10 +6227,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>568999</v>
+        <v>569019</v>
       </c>
       <c r="R51" t="n">
-        <v>6412852</v>
+        <v>6412826</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6286,13 +6289,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134260879</t>
+          <t>https://artportalen.se/Sighting/134260861</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134260905</v>
+        <v>134260879</v>
       </c>
       <c r="B52" t="n">
         <v>99195</v>
@@ -6335,10 +6338,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569004</v>
+        <v>568999</v>
       </c>
       <c r="R52" t="n">
-        <v>6412850</v>
+        <v>6412852</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6397,55 +6400,47 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134260905</t>
+          <t>https://artportalen.se/Sighting/134260879</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134260654</v>
+        <v>134260905</v>
       </c>
       <c r="B53" t="n">
-        <v>106324</v>
+        <v>99195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -6454,10 +6449,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569022</v>
+        <v>569004</v>
       </c>
       <c r="R53" t="n">
-        <v>6412800</v>
+        <v>6412850</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6492,11 +6487,6 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ca 10 knoppar/blommor</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6521,16 +6511,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134260654</t>
+          <t>https://artportalen.se/Sighting/134260905</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>74604083</v>
+        <v>134260654</v>
       </c>
       <c r="B54" t="n">
-        <v>97986</v>
+        <v>106324</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6538,37 +6528,53 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221946</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Västra bro 700 m V, Sm</t>
+          <t>A 48739, Karrum, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569033</v>
+        <v>569022</v>
       </c>
       <c r="R54" t="n">
-        <v>6412653</v>
+        <v>6412800</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6592,17 +6598,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>1987-12-31</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G2e 4012. SOM: Lycopodium clavatum. LEG: Gunvald Bruce</t>
+          <t>Ca 10 knoppar/blommor</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6611,31 +6617,139 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Barrskogsstig</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134260654</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>74604083</v>
+      </c>
+      <c r="B55" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Västra bro 700 m V, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>569033</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6412653</v>
+      </c>
+      <c r="S55" t="n">
+        <v>50</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>1983-01-01</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>1987-12-31</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7G2e 4012. SOM: Lycopodium clavatum. LEG: Gunvald Bruce</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Barrskogsstig</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
+      <c r="AX55" t="inlineStr">
         <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr">
+      <c r="AY55" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
+      <c r="AZ55" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/74604083</t>
         </is>
@@ -6696,6 +6810,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -2175,7 +2175,7 @@
         <v>129527917</v>
       </c>
       <c r="B15" t="n">
-        <v>58094</v>
+        <v>58096</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -2175,7 +2175,7 @@
         <v>129527917</v>
       </c>
       <c r="B15" t="n">
-        <v>58096</v>
+        <v>58097</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 48739-2025 artfynd.xlsx
+++ b/artfynd/A 48739-2025 artfynd.xlsx
@@ -2175,7 +2175,7 @@
         <v>129527917</v>
       </c>
       <c r="B15" t="n">
-        <v>58097</v>
+        <v>58101</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
